--- a/artfynd/A 31848-2019 artfynd.xlsx
+++ b/artfynd/A 31848-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31848-2019 artfynd.xlsx
+++ b/artfynd/A 31848-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,14 +800,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68625618</v>
+        <v>87908400</v>
       </c>
       <c r="B3" t="n">
         <v>96334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -837,19 +837,20 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsbråtberget, Vrm</t>
+          <t>Åsbråtberg, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383188.429047127</v>
+        <v>383151.7737921565</v>
       </c>
       <c r="R3" t="n">
-        <v>6694729.190321762</v>
+        <v>6694776.398747015</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,14 +872,9 @@
           <t>Fryksände</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Tor-0251</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -888,12 +884,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Under en låga i hyggeskant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,23 +903,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Storvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Malin Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -926,133 +918,7 @@
           <t>Malin Johansson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>87908400</v>
-      </c>
-      <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Åsbråtberg, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>383151.7737921565</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6694776.398747015</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Fryksände</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2020-08-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2020-08-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Under en låga i hyggeskant</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Malin Johansson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Malin Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
